--- a/docs/pitch-readiness.xlsx
+++ b/docs/pitch-readiness.xlsx
@@ -947,6 +947,38 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Landing page and marketing-site redesign</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Important for conversion and brand perception, but not the first platform blocker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/pitch-readiness.xlsx
+++ b/docs/pitch-readiness.xlsx
@@ -1,9 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookViews>
-    <workbookView/>
-  </workbookViews>
   <sheets>
     <sheet name="Pitch Readiness" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -15,7 +12,7 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,7 +46,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
